--- a/Data/final_tables/supplementary_table_1_BARD1_OddsRatios_table.xlsx
+++ b/Data/final_tables/supplementary_table_1_BARD1_OddsRatios_table.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.3226070576242304</v>
+        <v>0.3225858568782028</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.4882118872051144</v>
+        <v>0.4737180897649979</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -596,15 +596,15 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.2409017018624825</v>
+        <v>0.2408539569735484</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.94 (0.85-1.03)</t>
+          <t>0.93 (0.85-1.03)</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.1878134743010017</v>
+        <v>0.1794014200077941</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -648,19 +648,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.05 (1.83-8.96)</t>
+          <t>4.06 (1.83-8.98)</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.001633859726942945</v>
+        <v>0.001615540749509591</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.2 (0.99-1.46)</t>
+          <t>1.21 (1.0-1.47)</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.06493753910414671</v>
+        <v>0.05707496750871943</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.1628036662574706</v>
+        <v>0.1627702220432006</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.3150510324191255</v>
+        <v>0.3150140523691731</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -816,11 +816,11 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.23 (0.01-3.73)</t>
+          <t>0.22 (0.01-3.73)</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.2525776260972933</v>
+        <v>0.2526206687617462</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1.614976907397291e-33</v>
+        <v>1.754288317882203e-34</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.5124791769334636</v>
+        <v>0.5124726859725908</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.4397465240074101</v>
+        <v>0.4397066228794811</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.725317789299648</v>
+        <v>0.7253135524646543</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.4019597490941685</v>
+        <v>0.4019328498804886</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.7154113738522967</v>
+        <v>0.7154198752254525</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>2.004062070859862e-32</v>
+        <v>2.240412192208989e-33</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0.6554564814461403</v>
+        <v>0.6554567942059402</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.607971162233663</v>
+        <v>0.6078945536079718</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0.5015024439746867</v>
+        <v>0.5014835194689181</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.8737642773895898</v>
+        <v>0.87375072625107</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1152,19 +1152,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.15 (1.32-7.5)</t>
+          <t>3.16 (1.33-7.51)</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0.01510657350896634</v>
+        <v>0.01501929806880477</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.57 (0.43-0.74)</t>
+          <t>0.56 (0.43-0.73)</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1.068759231561878e-05</v>
+        <v>6.934356134795308e-06</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1208,11 +1208,11 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1.4 (0.69-2.8)</t>
+          <t>1.4 (0.69-2.81)</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.3867832796194279</v>
+        <v>0.3867625429597583</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7716306134097692</v>
+        <v>0.7716015961432888</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1268,15 +1268,15 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.4711448206632917</v>
+        <v>0.4711200626597214</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.95 (0.82-1.08)</t>
+          <t>0.94 (0.82-1.08)</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.4419299137010547</v>
+        <v>0.4216011474029481</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1320,19 +1320,19 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.6 (1.58-8.23)</t>
+          <t>3.61 (1.58-8.24)</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0.005154533683322766</v>
+        <v>0.005111915152530648</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.68 (0.53-0.87)</t>
+          <t>0.67 (0.52-0.86)</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.00154895359176286</v>
+        <v>0.001100175437444608</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.6360589113863773</v>
+        <v>0.6360506960686709</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.3221201975606058</v>
+        <v>0.3219960614852803</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0.3301142106093055</v>
+        <v>0.330085576238816</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.08308505311856974</v>
+        <v>0.08292395574987674</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1492,15 +1492,15 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0.7154113738522967</v>
+        <v>0.7154198752254525</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.35 (0.25-0.49)</t>
+          <t>0.34 (0.24-0.48)</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>9.972033778249039e-13</v>
+        <v>3.889087935647641e-13</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1552,11 +1552,11 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.45 (0.02-13.52)</t>
+          <t>0.45 (0.02-13.51)</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.4755704644595006</v>
+        <v>0.4755635110050385</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0.8708398648035731</v>
+        <v>0.8708379071874399</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>0.7154113738522967</v>
+        <v>0.7154198752254525</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>2.709721763411557e-41</v>
+        <v>2.719555649122525e-42</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1712,11 +1712,11 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.13 (1.38-3.29)</t>
+          <t>2.14 (1.38-3.29)</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>0.0003914898225370895</v>
+        <v>0.0003901414972923814</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.6445350056240053</v>
+        <v>0.6240897618485197</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0.005961495485255401</v>
+        <v>0.00595397313421986</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.4562640408445658</v>
+        <v>0.4378312192976714</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1824,19 +1824,19 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>6.19 (0.76-50.3)</t>
+          <t>6.19 (0.76-50.31)</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0.07445219212602244</v>
+        <v>0.0744456621407775</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.76 (0.56-1.03)</t>
+          <t>0.75 (0.56-1.03)</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.07299092375667891</v>
+        <v>0.07293582164332332</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1880,19 +1880,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>7.27 (0.89-59.08)</t>
+          <t>7.27 (0.89-59.09)</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0.03576073743865427</v>
+        <v>0.03575065036974413</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.76 (0.55-1.04)</t>
+          <t>0.75 (0.55-1.04)</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.0887246736350078</v>
+        <v>0.08866572379315438</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1936,11 +1936,11 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>7.07 (1.63-30.76)</t>
+          <t>7.07 (1.63-30.77)</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0.001789206064041027</v>
+        <v>0.001787386521294958</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.8387021143086167</v>
+        <v>0.8386989558976914</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -1992,11 +1992,11 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>6.75 (1.52-29.91)</t>
+          <t>6.75 (1.52-29.92)</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0.003601775021850573</v>
+        <v>0.003598781405460713</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.942026303990013</v>
+        <v>0.9420257264402213</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>0.07842322022575923</v>
+        <v>0.07841152812464353</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.2528646886659039</v>
+        <v>0.2306123129506751</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0.6400163153212011</v>
+        <v>0.6400133586349528</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.7094862447453387</v>
+        <v>0.7094832436403746</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0.0003252321435773081</v>
+        <v>0.0003243195942773991</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.8484539330284671</v>
+        <v>0.8484473389500937</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>0.008475939357638365</v>
+        <v>0.008464135298906602</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.5394371689781419</v>
+        <v>0.5394055700970635</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>0.4672775844353211</v>
+        <v>0.467277009685396</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.1621385997575917</v>
+        <v>0.1620704664185982</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>0.2586730222110951</v>
+        <v>0.2586568079965191</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.1395886658709387</v>
+        <v>0.1395451922909052</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2384,11 +2384,11 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2.55 (1.49-4.37)</t>
+          <t>2.56 (1.5-4.37)</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0.0004275499216491426</v>
+        <v>0.0004274665336222148</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>0.001677748274402553</v>
+        <v>0.001673637898035417</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0.003124934066074294</v>
+        <v>0.00312401449120902</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.5410616604028184</v>
+        <v>0.5410448320649163</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0.009761027862927318</v>
+        <v>0.009756918660313771</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.5501824510822202</v>
+        <v>0.5501640664482953</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0.0635612054843895</v>
+        <v>0.06355706831112229</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.3549379674597086</v>
+        <v>0.3393250292236844</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -2664,11 +2664,11 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1.25 (0.75-2.09)</t>
+          <t>1.26 (0.75-2.09)</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0.4388720879615608</v>
+        <v>0.4388680542432448</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.8409677787180232</v>
+        <v>0.8409646063315552</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0.3091152749195752</v>
+        <v>0.3091011434441487</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.08010487414015813</v>
+        <v>0.08003720514370938</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -2780,15 +2780,15 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0.1317787070408102</v>
+        <v>0.1317659113136566</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.87 (0.76-0.98)</t>
+          <t>0.86 (0.76-0.98)</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.02701644836472244</v>
+        <v>0.02696566539432369</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -2832,19 +2832,19 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>1.82 (1.29-2.57)</t>
+          <t>1.82 (1.3-2.57)</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0.0005235257631555407</v>
+        <v>0.0005232127708819259</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.96 (0.9-1.04)</t>
+          <t>0.96 (0.9-1.03)</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>0.3219808098743477</v>
+        <v>0.3131901016443614</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>0.003741190235494418</v>
+        <v>0.003738252294779071</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.1813084710383718</v>
+        <v>0.1689821017094594</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>0.005809188042755499</v>
+        <v>0.005807709175119231</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.4717715529132894</v>
+        <v>0.4717687631736504</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0.01055371444153883</v>
+        <v>0.01054454337383432</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0.153684184993374</v>
+        <v>0.1536765351317469</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.02291922339128761</v>
+        <v>0.02291173446478265</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0.0883310672484553</v>
+        <v>0.08832074201223516</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.05003149692229729</v>
+        <v>0.05001669222149506</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0.00046534560063148</v>
+        <v>0.0004650787249593193</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.6397938304987386</v>
+        <v>0.6397481343976195</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0.0097652207222705</v>
+        <v>0.009756287587853225</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.3664915356481142</v>
+        <v>0.3526841308294033</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
